--- a/artfynd/A 19337-2024 artfynd.xlsx
+++ b/artfynd/A 19337-2024 artfynd.xlsx
@@ -1532,7 +1532,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117414795</v>
+        <v>117414836</v>
       </c>
       <c r="B10" t="n">
         <v>102747</v>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511862</v>
+        <v>511978</v>
       </c>
       <c r="R10" t="n">
-        <v>6962379</v>
+        <v>6962251</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117414809</v>
+        <v>117414782</v>
       </c>
       <c r="B11" t="n">
-        <v>97742</v>
+        <v>103338</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,16 +1655,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>504</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511884</v>
+        <v>511808</v>
       </c>
       <c r="R11" t="n">
-        <v>6962374</v>
+        <v>6962323</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117414755</v>
+        <v>117414773</v>
       </c>
       <c r="B12" t="n">
         <v>97742</v>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511719</v>
+        <v>511797</v>
       </c>
       <c r="R12" t="n">
-        <v>6962286</v>
+        <v>6962294</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,10 +1853,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117414797</v>
+        <v>117414755</v>
       </c>
       <c r="B13" t="n">
-        <v>98170</v>
+        <v>97742</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1869,21 +1869,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219880</v>
+        <v>504</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511862</v>
+        <v>511719</v>
       </c>
       <c r="R13" t="n">
-        <v>6962379</v>
+        <v>6962286</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117414874</v>
+        <v>117414809</v>
       </c>
       <c r="B14" t="n">
         <v>97742</v>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511953</v>
+        <v>511884</v>
       </c>
       <c r="R14" t="n">
-        <v>6962218</v>
+        <v>6962374</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117414773</v>
+        <v>117414797</v>
       </c>
       <c r="B15" t="n">
-        <v>97742</v>
+        <v>98170</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2083,21 +2083,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>504</v>
+        <v>219880</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511797</v>
+        <v>511862</v>
       </c>
       <c r="R15" t="n">
-        <v>6962294</v>
+        <v>6962379</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117414845</v>
+        <v>117414820</v>
       </c>
       <c r="B16" t="n">
-        <v>90499</v>
+        <v>102747</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2186,30 +2186,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>222002</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2217,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511934</v>
+        <v>512008</v>
       </c>
       <c r="R16" t="n">
-        <v>6962237</v>
+        <v>6962332</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,10 +2388,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117414767</v>
+        <v>117414845</v>
       </c>
       <c r="B18" t="n">
-        <v>97742</v>
+        <v>90499</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2399,31 +2400,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>504</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511728</v>
+        <v>511934</v>
       </c>
       <c r="R18" t="n">
-        <v>6962340</v>
+        <v>6962237</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117414836</v>
+        <v>117414790</v>
       </c>
       <c r="B19" t="n">
-        <v>102747</v>
+        <v>97742</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,16 +2510,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222002</v>
+        <v>504</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511978</v>
+        <v>511799</v>
       </c>
       <c r="R19" t="n">
-        <v>6962251</v>
+        <v>6962369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117414790</v>
+        <v>117414795</v>
       </c>
       <c r="B20" t="n">
-        <v>97742</v>
+        <v>102747</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2617,16 +2617,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>504</v>
+        <v>222002</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511799</v>
+        <v>511862</v>
       </c>
       <c r="R20" t="n">
-        <v>6962369</v>
+        <v>6962379</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117414782</v>
+        <v>117414874</v>
       </c>
       <c r="B21" t="n">
-        <v>103338</v>
+        <v>97742</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,16 +2724,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222412</v>
+        <v>504</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511808</v>
+        <v>511953</v>
       </c>
       <c r="R21" t="n">
-        <v>6962323</v>
+        <v>6962218</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117414820</v>
+        <v>117414767</v>
       </c>
       <c r="B22" t="n">
-        <v>102747</v>
+        <v>97742</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222002</v>
+        <v>504</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512008</v>
+        <v>511728</v>
       </c>
       <c r="R22" t="n">
-        <v>6962332</v>
+        <v>6962340</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 19337-2024 artfynd.xlsx
+++ b/artfynd/A 19337-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116361497</v>
+        <v>116979189</v>
       </c>
       <c r="B2" t="n">
-        <v>57293</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512090</v>
+        <v>511681</v>
       </c>
       <c r="R2" t="n">
-        <v>6962234</v>
+        <v>6962334</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,17 +752,13 @@
           <t>2024-04-22</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Basalt hack i levande träd. Färskt</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116361477</v>
+        <v>117414755</v>
       </c>
       <c r="B3" t="n">
-        <v>100017</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511769</v>
+        <v>511719</v>
       </c>
       <c r="R3" t="n">
-        <v>6962327</v>
+        <v>6962286</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116979189</v>
+        <v>117414767</v>
       </c>
       <c r="B4" t="n">
-        <v>95327</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511681</v>
+        <v>511728</v>
       </c>
       <c r="R4" t="n">
-        <v>6962334</v>
+        <v>6962340</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,12 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,42 +981,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116979196</v>
+        <v>117414773</v>
       </c>
       <c r="B5" t="n">
-        <v>90470</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1043,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511716</v>
+        <v>511797</v>
       </c>
       <c r="R5" t="n">
-        <v>6962348</v>
+        <v>6962294</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,12 +1050,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116979272</v>
+        <v>117414790</v>
       </c>
       <c r="B6" t="n">
-        <v>91383</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,26 +1094,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1149,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511868</v>
+        <v>511799</v>
       </c>
       <c r="R6" t="n">
-        <v>6962383</v>
+        <v>6962369</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,12 +1152,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,42 +1185,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116979193</v>
+        <v>117414809</v>
       </c>
       <c r="B7" t="n">
-        <v>82219</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>504</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1255,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511698</v>
+        <v>511884</v>
       </c>
       <c r="R7" t="n">
-        <v>6962330</v>
+        <v>6962374</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,12 +1254,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116979267</v>
+        <v>117414874</v>
       </c>
       <c r="B8" t="n">
-        <v>100040</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1334,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>504</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511773</v>
+        <v>511953</v>
       </c>
       <c r="R8" t="n">
-        <v>6962326</v>
+        <v>6962218</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,12 +1356,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,43 +1389,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116979280</v>
+        <v>117414845</v>
       </c>
       <c r="B9" t="n">
-        <v>100040</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1469,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511953</v>
+        <v>511934</v>
       </c>
       <c r="R9" t="n">
-        <v>6962254</v>
+        <v>6962237</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,12 +1457,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,43 +1490,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117414836</v>
+        <v>116979296</v>
       </c>
       <c r="B10" t="n">
-        <v>102747</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222002</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1576,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511978</v>
+        <v>511737</v>
       </c>
       <c r="R10" t="n">
-        <v>6962251</v>
+        <v>6962387</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,12 +1558,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,43 +1591,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117414782</v>
+        <v>116979193</v>
       </c>
       <c r="B11" t="n">
-        <v>103338</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1683,10 +1629,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511808</v>
+        <v>511698</v>
       </c>
       <c r="R11" t="n">
-        <v>6962323</v>
+        <v>6962330</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,12 +1659,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,43 +1692,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117414773</v>
+        <v>116979475</v>
       </c>
       <c r="B12" t="n">
-        <v>97742</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>504</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1790,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511797</v>
+        <v>511751</v>
       </c>
       <c r="R12" t="n">
-        <v>6962294</v>
+        <v>6962408</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,12 +1760,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1853,15 +1793,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117414755</v>
+        <v>116979272</v>
       </c>
       <c r="B13" t="n">
-        <v>97742</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,27 +1804,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>504</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1897,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511719</v>
+        <v>511868</v>
       </c>
       <c r="R13" t="n">
-        <v>6962286</v>
+        <v>6962383</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,12 +1861,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1960,15 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117414809</v>
+        <v>116361497</v>
       </c>
       <c r="B14" t="n">
-        <v>97742</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1976,27 +1905,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>504</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2004,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511884</v>
+        <v>512090</v>
       </c>
       <c r="R14" t="n">
-        <v>6962374</v>
+        <v>6962234</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,12 +1963,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Basalt hack i levande träd. Färskt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2048,7 +1982,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2067,43 +2000,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117414797</v>
+        <v>116979200</v>
       </c>
       <c r="B15" t="n">
-        <v>98170</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219880</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2111,10 +2039,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511862</v>
+        <v>511743</v>
       </c>
       <c r="R15" t="n">
-        <v>6962379</v>
+        <v>6962303</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,12 +2069,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2155,7 +2083,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2174,15 +2101,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117414820</v>
+        <v>117414797</v>
       </c>
       <c r="B16" t="n">
-        <v>102747</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2190,21 +2112,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222002</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2140,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>512008</v>
+        <v>511862</v>
       </c>
       <c r="R16" t="n">
-        <v>6962332</v>
+        <v>6962379</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2281,15 +2203,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117414837</v>
+        <v>117414795</v>
       </c>
       <c r="B17" t="n">
-        <v>100097</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2297,21 +2214,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2242,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511978</v>
+        <v>511862</v>
       </c>
       <c r="R17" t="n">
-        <v>6962251</v>
+        <v>6962379</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2388,42 +2305,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117414845</v>
+        <v>117414820</v>
       </c>
       <c r="B18" t="n">
-        <v>90499</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>222002</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2431,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511934</v>
+        <v>512008</v>
       </c>
       <c r="R18" t="n">
-        <v>6962237</v>
+        <v>6962332</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,15 +2407,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117414790</v>
+        <v>117414836</v>
       </c>
       <c r="B19" t="n">
-        <v>97742</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2510,16 +2418,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>504</v>
+        <v>222002</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2538,10 +2446,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511799</v>
+        <v>511978</v>
       </c>
       <c r="R19" t="n">
-        <v>6962369</v>
+        <v>6962251</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,15 +2509,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117414795</v>
+        <v>117414782</v>
       </c>
       <c r="B20" t="n">
-        <v>102747</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2617,16 +2520,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222002</v>
+        <v>222412</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2645,10 +2548,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511862</v>
+        <v>511808</v>
       </c>
       <c r="R20" t="n">
-        <v>6962379</v>
+        <v>6962323</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,15 +2611,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117414874</v>
+        <v>116361477</v>
       </c>
       <c r="B21" t="n">
-        <v>97742</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,21 +2622,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>504</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2752,10 +2650,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511953</v>
+        <v>511769</v>
       </c>
       <c r="R21" t="n">
-        <v>6962218</v>
+        <v>6962327</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2782,12 +2680,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,15 +2713,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117414767</v>
+        <v>116979267</v>
       </c>
       <c r="B22" t="n">
-        <v>97742</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2831,21 +2724,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>504</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2859,10 +2752,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511728</v>
+        <v>511773</v>
       </c>
       <c r="R22" t="n">
-        <v>6962340</v>
+        <v>6962326</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2889,12 +2782,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2919,6 +2812,210 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>116979280</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vikängsviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>511953</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6962254</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>117414837</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vikängsviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>511978</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6962251</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19337-2024 artfynd.xlsx
+++ b/artfynd/A 19337-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116979189</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117414755</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117414767</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117414773</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117414790</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117414809</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117414874</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1487,6 +1527,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117414845</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1588,6 +1633,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116979296</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1689,6 +1739,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116979193</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1790,6 +1845,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116979475</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1891,6 +1951,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116979272</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1997,6 +2062,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116361497</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2098,6 +2168,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116979200</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2200,6 +2275,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117414797</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2302,6 +2382,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117414795</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2404,6 +2489,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117414820</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2506,6 +2596,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117414836</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2608,6 +2703,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117414782</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2710,6 +2810,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116361477</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2812,6 +2917,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116979267</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2914,6 +3024,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116979280</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3016,8 +3131,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117414837</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>